--- a/01_Reporting_Suite/Data_SiteIQ/DAILY_SUMMARY.xlsx
+++ b/01_Reporting_Suite/Data_SiteIQ/DAILY_SUMMARY.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
   <si>
     <t>PROJECT SCHEDULE</t>
   </si>
@@ -33,10 +33,10 @@
     <t>Gladstone k2 2026 Shutdown</t>
   </si>
   <si>
-    <t>13/07/2026 01:07 PM</t>
-  </si>
-  <si>
-    <t>27/07/2026 01:07 PM</t>
+    <t>13/07/2026 05:42 AM</t>
+  </si>
+  <si>
+    <t>29/07/2026 05:42 AM</t>
   </si>
   <si>
     <t>Andrew Fisher</t>
@@ -112,6 +112,9 @@
   </si>
   <si>
     <t>TOTAL FOR: 26/07/2026</t>
+  </si>
+  <si>
+    <t>TOTAL FOR: 27/07/2026</t>
   </si>
   <si>
     <t>REPORT TOTAL:</t>
@@ -164,8 +167,8 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="27.1918983459473" customWidth="1"/>
-    <col min="2" max="2" width="20.7179412841797" customWidth="1"/>
-    <col min="3" max="3" width="20.7179412841797" customWidth="1"/>
+    <col min="2" max="2" width="20.8519611358643" customWidth="1"/>
+    <col min="3" max="3" width="20.8519611358643" customWidth="1"/>
     <col min="4" max="4" width="15.2527256011963" customWidth="1"/>
     <col min="5" max="5" width="35.4623603820801" customWidth="1"/>
   </cols>
@@ -211,11 +214,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:M13"/>
+  <dimension ref="A1:M14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="22.6638088226318" customWidth="1"/>
-    <col min="2" max="2" width="9.140625" customWidth="1"/>
+    <col min="2" max="2" width="9.6135892868042" customWidth="1"/>
     <col min="3" max="3" width="12.0372314453125" customWidth="1"/>
     <col min="4" max="4" width="9.140625" customWidth="1"/>
     <col min="5" max="5" width="9.140625" customWidth="1"/>
@@ -726,40 +729,81 @@
         <v>33</v>
       </c>
       <c r="B13" s="0">
-        <v>64606.9</v>
+        <v>10324.67</v>
       </c>
       <c r="C13" s="0">
+        <v>0</v>
+      </c>
+      <c r="D13" s="0">
+        <v>0</v>
+      </c>
+      <c r="E13" s="0">
+        <v>0</v>
+      </c>
+      <c r="F13" s="0">
+        <v>0</v>
+      </c>
+      <c r="G13" s="0">
+        <v>0</v>
+      </c>
+      <c r="H13" s="0">
+        <v>0</v>
+      </c>
+      <c r="I13" s="0">
+        <v>0</v>
+      </c>
+      <c r="J13" s="0">
+        <v>0</v>
+      </c>
+      <c r="K13" s="0">
+        <v>0</v>
+      </c>
+      <c r="L13" s="0">
+        <v>0</v>
+      </c>
+      <c r="M13" s="0">
+        <v>10324.67</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="B14" s="0">
+        <v>74931.57</v>
+      </c>
+      <c r="C14" s="0">
         <v>45000</v>
       </c>
-      <c r="D13" s="0">
+      <c r="D14" s="0">
         <v>58520</v>
       </c>
-      <c r="E13" s="0">
+      <c r="E14" s="0">
         <v>15605</v>
       </c>
-      <c r="F13" s="0">
-        <v>0</v>
-      </c>
-      <c r="G13" s="0">
-        <v>0</v>
-      </c>
-      <c r="H13" s="0">
-        <v>0</v>
-      </c>
-      <c r="I13" s="0">
-        <v>0</v>
-      </c>
-      <c r="J13" s="0">
-        <v>0</v>
-      </c>
-      <c r="K13" s="0">
-        <v>0</v>
-      </c>
-      <c r="L13" s="0">
-        <v>0</v>
-      </c>
-      <c r="M13" s="0">
-        <v>183731.9</v>
+      <c r="F14" s="0">
+        <v>0</v>
+      </c>
+      <c r="G14" s="0">
+        <v>0</v>
+      </c>
+      <c r="H14" s="0">
+        <v>0</v>
+      </c>
+      <c r="I14" s="0">
+        <v>0</v>
+      </c>
+      <c r="J14" s="0">
+        <v>0</v>
+      </c>
+      <c r="K14" s="0">
+        <v>0</v>
+      </c>
+      <c r="L14" s="0">
+        <v>0</v>
+      </c>
+      <c r="M14" s="0">
+        <v>194056.57</v>
       </c>
     </row>
   </sheetData>

--- a/01_Reporting_Suite/Data_SiteIQ/DAILY_SUMMARY.xlsx
+++ b/01_Reporting_Suite/Data_SiteIQ/DAILY_SUMMARY.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
   <si>
     <t>PROJECT SCHEDULE</t>
   </si>
@@ -33,10 +33,10 @@
     <t>Gladstone k2 2026 Shutdown</t>
   </si>
   <si>
-    <t>13/07/2026 05:42 AM</t>
-  </si>
-  <si>
-    <t>29/07/2026 05:42 AM</t>
+    <t>13/07/2026 06:41 AM</t>
+  </si>
+  <si>
+    <t>03/08/2026 06:41 AM</t>
   </si>
   <si>
     <t>Andrew Fisher</t>
@@ -115,6 +115,21 @@
   </si>
   <si>
     <t>TOTAL FOR: 27/07/2026</t>
+  </si>
+  <si>
+    <t>TOTAL FOR: 28/07/2026</t>
+  </si>
+  <si>
+    <t>TOTAL FOR: 29/07/2026</t>
+  </si>
+  <si>
+    <t>TOTAL FOR: 30/07/2026</t>
+  </si>
+  <si>
+    <t>TOTAL FOR: 31/07/2026</t>
+  </si>
+  <si>
+    <t>TOTAL FOR: 01/08/2026</t>
   </si>
   <si>
     <t>REPORT TOTAL:</t>
@@ -214,14 +229,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:M14"/>
+  <dimension ref="A1:M19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="22.6638088226318" customWidth="1"/>
-    <col min="2" max="2" width="9.6135892868042" customWidth="1"/>
+    <col min="2" max="2" width="10.7072458267212" customWidth="1"/>
     <col min="3" max="3" width="12.0372314453125" customWidth="1"/>
     <col min="4" max="4" width="9.140625" customWidth="1"/>
-    <col min="5" max="5" width="9.140625" customWidth="1"/>
+    <col min="5" max="5" width="9.6135892868042" customWidth="1"/>
     <col min="6" max="6" width="13.991286277771" customWidth="1"/>
     <col min="7" max="7" width="9.50002956390381" customWidth="1"/>
     <col min="8" max="8" width="9.96756935119629" customWidth="1"/>
@@ -770,40 +785,245 @@
         <v>34</v>
       </c>
       <c r="B14" s="0">
-        <v>74931.57</v>
+        <v>10397.13</v>
       </c>
       <c r="C14" s="0">
-        <v>45000</v>
+        <v>1134</v>
       </c>
       <c r="D14" s="0">
+        <v>0</v>
+      </c>
+      <c r="E14" s="0">
+        <v>1206.96</v>
+      </c>
+      <c r="F14" s="0">
+        <v>0</v>
+      </c>
+      <c r="G14" s="0">
+        <v>0</v>
+      </c>
+      <c r="H14" s="0">
+        <v>0</v>
+      </c>
+      <c r="I14" s="0">
+        <v>0</v>
+      </c>
+      <c r="J14" s="0">
+        <v>0</v>
+      </c>
+      <c r="K14" s="0">
+        <v>0</v>
+      </c>
+      <c r="L14" s="0">
+        <v>0</v>
+      </c>
+      <c r="M14" s="0">
+        <v>12738.09</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="B15" s="0">
+        <v>11180.75</v>
+      </c>
+      <c r="C15" s="0">
+        <v>0</v>
+      </c>
+      <c r="D15" s="0">
+        <v>0</v>
+      </c>
+      <c r="E15" s="0">
+        <v>0</v>
+      </c>
+      <c r="F15" s="0">
+        <v>0</v>
+      </c>
+      <c r="G15" s="0">
+        <v>0</v>
+      </c>
+      <c r="H15" s="0">
+        <v>0</v>
+      </c>
+      <c r="I15" s="0">
+        <v>0</v>
+      </c>
+      <c r="J15" s="0">
+        <v>0</v>
+      </c>
+      <c r="K15" s="0">
+        <v>0</v>
+      </c>
+      <c r="L15" s="0">
+        <v>0</v>
+      </c>
+      <c r="M15" s="0">
+        <v>11180.75</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="B16" s="0">
+        <v>11803.52</v>
+      </c>
+      <c r="C16" s="0">
+        <v>0</v>
+      </c>
+      <c r="D16" s="0">
+        <v>0</v>
+      </c>
+      <c r="E16" s="0">
+        <v>0</v>
+      </c>
+      <c r="F16" s="0">
+        <v>0</v>
+      </c>
+      <c r="G16" s="0">
+        <v>0</v>
+      </c>
+      <c r="H16" s="0">
+        <v>0</v>
+      </c>
+      <c r="I16" s="0">
+        <v>0</v>
+      </c>
+      <c r="J16" s="0">
+        <v>0</v>
+      </c>
+      <c r="K16" s="0">
+        <v>0</v>
+      </c>
+      <c r="L16" s="0">
+        <v>0</v>
+      </c>
+      <c r="M16" s="0">
+        <v>11803.52</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="B17" s="0">
+        <v>11043.36</v>
+      </c>
+      <c r="C17" s="0">
+        <v>0</v>
+      </c>
+      <c r="D17" s="0">
+        <v>0</v>
+      </c>
+      <c r="E17" s="0">
+        <v>0</v>
+      </c>
+      <c r="F17" s="0">
+        <v>0</v>
+      </c>
+      <c r="G17" s="0">
+        <v>0</v>
+      </c>
+      <c r="H17" s="0">
+        <v>0</v>
+      </c>
+      <c r="I17" s="0">
+        <v>0</v>
+      </c>
+      <c r="J17" s="0">
+        <v>0</v>
+      </c>
+      <c r="K17" s="0">
+        <v>0</v>
+      </c>
+      <c r="L17" s="0">
+        <v>0</v>
+      </c>
+      <c r="M17" s="0">
+        <v>11043.36</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="0" t="s">
+        <v>38</v>
+      </c>
+      <c r="B18" s="0">
+        <v>11052.68</v>
+      </c>
+      <c r="C18" s="0">
+        <v>0</v>
+      </c>
+      <c r="D18" s="0">
+        <v>0</v>
+      </c>
+      <c r="E18" s="0">
+        <v>0</v>
+      </c>
+      <c r="F18" s="0">
+        <v>0</v>
+      </c>
+      <c r="G18" s="0">
+        <v>0</v>
+      </c>
+      <c r="H18" s="0">
+        <v>0</v>
+      </c>
+      <c r="I18" s="0">
+        <v>0</v>
+      </c>
+      <c r="J18" s="0">
+        <v>0</v>
+      </c>
+      <c r="K18" s="0">
+        <v>0</v>
+      </c>
+      <c r="L18" s="0">
+        <v>0</v>
+      </c>
+      <c r="M18" s="0">
+        <v>11052.68</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="B19" s="0">
+        <v>130409.01</v>
+      </c>
+      <c r="C19" s="0">
+        <v>46134</v>
+      </c>
+      <c r="D19" s="0">
         <v>58520</v>
       </c>
-      <c r="E14" s="0">
-        <v>15605</v>
-      </c>
-      <c r="F14" s="0">
-        <v>0</v>
-      </c>
-      <c r="G14" s="0">
-        <v>0</v>
-      </c>
-      <c r="H14" s="0">
-        <v>0</v>
-      </c>
-      <c r="I14" s="0">
-        <v>0</v>
-      </c>
-      <c r="J14" s="0">
-        <v>0</v>
-      </c>
-      <c r="K14" s="0">
-        <v>0</v>
-      </c>
-      <c r="L14" s="0">
-        <v>0</v>
-      </c>
-      <c r="M14" s="0">
-        <v>194056.57</v>
+      <c r="E19" s="0">
+        <v>16811.96</v>
+      </c>
+      <c r="F19" s="0">
+        <v>0</v>
+      </c>
+      <c r="G19" s="0">
+        <v>0</v>
+      </c>
+      <c r="H19" s="0">
+        <v>0</v>
+      </c>
+      <c r="I19" s="0">
+        <v>0</v>
+      </c>
+      <c r="J19" s="0">
+        <v>0</v>
+      </c>
+      <c r="K19" s="0">
+        <v>0</v>
+      </c>
+      <c r="L19" s="0">
+        <v>0</v>
+      </c>
+      <c r="M19" s="0">
+        <v>251874.97</v>
       </c>
     </row>
   </sheetData>

--- a/01_Reporting_Suite/Data_SiteIQ/DAILY_SUMMARY.xlsx
+++ b/01_Reporting_Suite/Data_SiteIQ/DAILY_SUMMARY.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
   <si>
     <t>PROJECT SCHEDULE</t>
   </si>
@@ -33,10 +33,10 @@
     <t>Gladstone k2 2026 Shutdown</t>
   </si>
   <si>
-    <t>13/07/2026 06:41 AM</t>
-  </si>
-  <si>
-    <t>03/08/2026 06:41 AM</t>
+    <t>13/07/2026 07:54 AM</t>
+  </si>
+  <si>
+    <t>05/08/2026 07:54 AM</t>
   </si>
   <si>
     <t>Andrew Fisher</t>
@@ -130,6 +130,12 @@
   </si>
   <si>
     <t>TOTAL FOR: 01/08/2026</t>
+  </si>
+  <si>
+    <t>TOTAL FOR: 02/08/2026</t>
+  </si>
+  <si>
+    <t>TOTAL FOR: 03/08/2026</t>
   </si>
   <si>
     <t>REPORT TOTAL:</t>
@@ -229,7 +235,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:M19"/>
+  <dimension ref="A1:M21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="22.6638088226318" customWidth="1"/>
@@ -990,40 +996,122 @@
         <v>39</v>
       </c>
       <c r="B19" s="0">
-        <v>130409.01</v>
+        <v>11315.06</v>
       </c>
       <c r="C19" s="0">
+        <v>0</v>
+      </c>
+      <c r="D19" s="0">
+        <v>0</v>
+      </c>
+      <c r="E19" s="0">
+        <v>0</v>
+      </c>
+      <c r="F19" s="0">
+        <v>0</v>
+      </c>
+      <c r="G19" s="0">
+        <v>0</v>
+      </c>
+      <c r="H19" s="0">
+        <v>0</v>
+      </c>
+      <c r="I19" s="0">
+        <v>0</v>
+      </c>
+      <c r="J19" s="0">
+        <v>0</v>
+      </c>
+      <c r="K19" s="0">
+        <v>0</v>
+      </c>
+      <c r="L19" s="0">
+        <v>0</v>
+      </c>
+      <c r="M19" s="0">
+        <v>11315.06</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="B20" s="0">
+        <v>11139.06</v>
+      </c>
+      <c r="C20" s="0">
+        <v>0</v>
+      </c>
+      <c r="D20" s="0">
+        <v>0</v>
+      </c>
+      <c r="E20" s="0">
+        <v>0</v>
+      </c>
+      <c r="F20" s="0">
+        <v>0</v>
+      </c>
+      <c r="G20" s="0">
+        <v>0</v>
+      </c>
+      <c r="H20" s="0">
+        <v>0</v>
+      </c>
+      <c r="I20" s="0">
+        <v>0</v>
+      </c>
+      <c r="J20" s="0">
+        <v>0</v>
+      </c>
+      <c r="K20" s="0">
+        <v>0</v>
+      </c>
+      <c r="L20" s="0">
+        <v>0</v>
+      </c>
+      <c r="M20" s="0">
+        <v>11139.06</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="B21" s="0">
+        <v>152863.13</v>
+      </c>
+      <c r="C21" s="0">
         <v>46134</v>
       </c>
-      <c r="D19" s="0">
+      <c r="D21" s="0">
         <v>58520</v>
       </c>
-      <c r="E19" s="0">
+      <c r="E21" s="0">
         <v>16811.96</v>
       </c>
-      <c r="F19" s="0">
-        <v>0</v>
-      </c>
-      <c r="G19" s="0">
-        <v>0</v>
-      </c>
-      <c r="H19" s="0">
-        <v>0</v>
-      </c>
-      <c r="I19" s="0">
-        <v>0</v>
-      </c>
-      <c r="J19" s="0">
-        <v>0</v>
-      </c>
-      <c r="K19" s="0">
-        <v>0</v>
-      </c>
-      <c r="L19" s="0">
-        <v>0</v>
-      </c>
-      <c r="M19" s="0">
-        <v>251874.97</v>
+      <c r="F21" s="0">
+        <v>0</v>
+      </c>
+      <c r="G21" s="0">
+        <v>0</v>
+      </c>
+      <c r="H21" s="0">
+        <v>0</v>
+      </c>
+      <c r="I21" s="0">
+        <v>0</v>
+      </c>
+      <c r="J21" s="0">
+        <v>0</v>
+      </c>
+      <c r="K21" s="0">
+        <v>0</v>
+      </c>
+      <c r="L21" s="0">
+        <v>0</v>
+      </c>
+      <c r="M21" s="0">
+        <v>274329.09</v>
       </c>
     </row>
   </sheetData>
